--- a/Datas/Level.xlsx
+++ b/Datas/Level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14415" windowHeight="8070"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="15">
   <si>
     <t>##var</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>list,int</t>
+  </si>
+  <si>
+    <t>10001,10002,10002,10002,10002,10002,10003</t>
   </si>
   <si>
     <t>10001,10001,10001,10002,10002,10002,10003</t>
@@ -1320,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1334,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1348,7 +1351,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1362,7 +1365,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1376,7 +1379,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1390,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1404,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1418,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1432,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1446,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1460,7 +1463,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1474,7 +1477,7 @@
         <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1488,7 +1491,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -1502,7 +1505,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -1516,7 +1519,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -1530,7 +1533,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -1544,7 +1547,7 @@
         <v>18</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -1558,7 +1561,7 @@
         <v>19</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -1572,7 +1575,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -1586,7 +1589,7 @@
         <v>21</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -1600,7 +1603,7 @@
         <v>22</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -1614,7 +1617,7 @@
         <v>23</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -1628,7 +1631,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -1642,7 +1645,7 @@
         <v>25</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -1656,7 +1659,7 @@
         <v>26</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -1670,7 +1673,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -1684,7 +1687,7 @@
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -1698,7 +1701,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="2:5">
@@ -1712,7 +1715,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
